--- a/fixtures/matching.xlsx
+++ b/fixtures/matching.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Περιφερειακές ενότητες</t>
   </si>
   <si>
-    <t xml:space="preserve">Στερεά Ελλάδα - Εύβοια//Βοιωτίας/, Πελοπόννησος//Αρκαδίας/, Kρήτη//Λασιθίου/, Νησιά Αιγαίου//Λέσβου</t>
+    <t xml:space="preserve">Στερεά Ελλάδα – Εύβοια//Βοιωτίας,, Πελοπόννησος//Αρκαδίας,, Kρήτη//Λασιθίου,, Νησιά Αιγαίου//Λέσβου</t>
   </si>
   <si>
     <t xml:space="preserve">CIVICS</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Role</t>
   </si>
   <si>
-    <t xml:space="preserve">Parliament//Legislates/, Supreme Court//Interprets law/, President//Head of state</t>
+    <t xml:space="preserve">Parliament//Legislates,, Supreme Court//Interprets law,, President//Head of state</t>
   </si>
   <si>
     <t xml:space="preserve">HISTORY</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Event</t>
   </si>
   <si>
-    <t xml:space="preserve">1821//Greek War of Independence/, 1940//OXI Day/, 1974//Restoration of Democracy</t>
+    <t xml:space="preserve">1821//Greek War of Independence,, 1940//OXI Day,, 1974//Restoration of Democracy</t>
   </si>
   <si>
     <t xml:space="preserve">CULTURE</t>
@@ -85,10 +85,7 @@
     <t xml:space="preserve">City</t>
   </si>
   <si>
-    <t xml:space="preserve">Parthenon//Athens/, White Tower//Thessaloniki/, Palace of Knossos//Heraklion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asda</t>
+    <t xml:space="preserve">Parthenon//Athens,, White Tower//Thessaloniki,, Palace of Knossos//Heraklion</t>
   </si>
 </sst>
 </file>
@@ -191,7 +188,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -549,9 +546,7 @@
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="F6" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/fixtures/matching.xlsx
+++ b/fixtures/matching.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Περιφερειακές ενότητες</t>
   </si>
   <si>
-    <t xml:space="preserve">Στερεά Ελλάδα – Εύβοια//Βοιωτίας,, Πελοπόννησος//Αρκαδίας,, Kρήτη//Λασιθίου,, Νησιά Αιγαίου//Λέσβου</t>
+    <t xml:space="preserve">Στερεά Ελλάδα – Εύβοια_Βοιωτίας | Πελοπόννησος_Αρκαδίας| Kρήτη_Λασιθίου| Νησιά Αιγαίου_Λέσβου</t>
   </si>
   <si>
     <t xml:space="preserve">CIVICS</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Role</t>
   </si>
   <si>
-    <t xml:space="preserve">Parliament//Legislates,, Supreme Court//Interprets law,, President//Head of state</t>
+    <t xml:space="preserve">Parliament_Legislates | Supreme Court_Interprets law | President_Head of state</t>
   </si>
   <si>
     <t xml:space="preserve">HISTORY</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Event</t>
   </si>
   <si>
-    <t xml:space="preserve">1821//Greek War of Independence,, 1940//OXI Day,, 1974//Restoration of Democracy</t>
+    <t xml:space="preserve">1821_Greek War of Independence| 1940_OXI Day|1974_Restoration of Democracy</t>
   </si>
   <si>
     <t xml:space="preserve">CULTURE</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">City</t>
   </si>
   <si>
-    <t xml:space="preserve">Parthenon//Athens,, White Tower//Thessaloniki,, Palace of Knossos//Heraklion</t>
+    <t xml:space="preserve">Parthenon_Athens|White Tower_Thessaloniki | Palace of Knossos_Heraklion</t>
   </si>
 </sst>
 </file>
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>6</v>
@@ -497,7 +497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -512,7 +512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
         <v>14</v>
@@ -527,7 +527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
         <v>18</v>
